--- a/Result/profitability/3617.xlsx
+++ b/Result/profitability/3617.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM73"/>
+  <dimension ref="A1:AM74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>4.33</v>
       </c>
       <c r="M2" t="n">
-        <v>4.445</v>
+        <v>4.65125</v>
       </c>
       <c r="N2" t="n">
-        <v>51.05</v>
+        <v>52.46125</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>1.68</v>
       </c>
       <c r="M3" t="n">
-        <v>3.9875</v>
+        <v>3.95125</v>
       </c>
       <c r="N3" t="n">
-        <v>43.5075</v>
+        <v>44.98125</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>1.46</v>
       </c>
       <c r="M4" t="n">
-        <v>3.26</v>
+        <v>3.58375</v>
       </c>
       <c r="N4" t="n">
-        <v>45.605</v>
+        <v>46.8875</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>0.72</v>
       </c>
       <c r="M5" t="n">
-        <v>2.8</v>
+        <v>3.65</v>
       </c>
       <c r="N5" t="n">
-        <v>42.79</v>
+        <v>43.85</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>1.66</v>
       </c>
       <c r="M6" t="n">
-        <v>2.98375</v>
+        <v>2.98</v>
       </c>
       <c r="N6" t="n">
-        <v>41.9525</v>
+        <v>42.8775</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>1.99</v>
       </c>
       <c r="M7" t="n">
-        <v>2.355</v>
+        <v>2.87</v>
       </c>
       <c r="N7" t="n">
-        <v>40.2775</v>
+        <v>41.68625</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.86</v>
       </c>
       <c r="M8" t="n">
-        <v>2.10375</v>
+        <v>2.46125</v>
       </c>
       <c r="N8" t="n">
-        <v>39.1975</v>
+        <v>40.32625</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -9699,6 +9699,133 @@
       </c>
       <c r="AM73" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>3617</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>3339</v>
+      </c>
+      <c r="D74" t="n">
+        <v>1239</v>
+      </c>
+      <c r="E74" t="n">
+        <v>2100</v>
+      </c>
+      <c r="F74" t="n">
+        <v>62.89</v>
+      </c>
+      <c r="G74" t="n">
+        <v>923</v>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>27.63%</t>
+        </is>
+      </c>
+      <c r="I74" t="n">
+        <v>-12</v>
+      </c>
+      <c r="J74" t="n">
+        <v>911</v>
+      </c>
+      <c r="K74" t="n">
+        <v>658</v>
+      </c>
+      <c r="L74" t="n">
+        <v>6.99</v>
+      </c>
+      <c r="M74" t="n">
+        <v>4.7775</v>
+      </c>
+      <c r="N74" t="n">
+        <v>54.2</v>
+      </c>
+      <c r="O74" t="n">
+        <v>1</v>
+      </c>
+      <c r="P74" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q74" t="n">
+        <v>0</v>
+      </c>
+      <c r="R74" t="n">
+        <v>1</v>
+      </c>
+      <c r="S74" t="n">
+        <v>1</v>
+      </c>
+      <c r="T74" t="n">
+        <v>0</v>
+      </c>
+      <c r="U74" t="n">
+        <v>1</v>
+      </c>
+      <c r="V74" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W74" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="X74" t="n">
+        <v>0.692493946731235</v>
+      </c>
+      <c r="Y74" t="n">
+        <v>9.030000000000001</v>
+      </c>
+      <c r="Z74" t="n">
+        <v>0.1676568882287413</v>
+      </c>
+      <c r="AA74" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AB74" t="n">
+        <v>35.78947368421053</v>
+      </c>
+      <c r="AC74" t="n">
+        <v>8.480000000000004</v>
+      </c>
+      <c r="AD74" t="n">
+        <v>0.1558537033633525</v>
+      </c>
+      <c r="AE74" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF74" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG74" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH74" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI74" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ74" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK74" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL74" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM74" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
